--- a/Attendance/Football/attendance_report.xlsx
+++ b/Attendance/Football/attendance_report.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karan</t>
+          <t>Prachi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,17 +496,59 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>❌ Poor</t>
+          <t>✅ Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dhruv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>✅ Good</t>
         </is>
       </c>
     </row>
